--- a/sources/yoshimitsu_step7.xlsx
+++ b/sources/yoshimitsu_step7.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA140"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -443,10 +443,11 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="12" customWidth="1" min="22" max="22"/>
     <col width="121" customWidth="1" min="23" max="23"/>
-    <col width="38" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
     <col width="38" customWidth="1" min="25" max="25"/>
     <col width="38" customWidth="1" min="26" max="26"/>
-    <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="38" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -574,20 +575,25 @@
       </c>
       <c r="X2" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y2" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y2" s="1" t="inlineStr">
+      <c r="Z2" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z2" s="1" t="inlineStr">
+      <c r="AA2" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA2" s="1" t="inlineStr">
+      <c r="AB2" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -649,12 +655,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>300d5f26-19ad-4418-ada3-84c2382a900d</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>f7658712-52dc-4c37-b2e6-831edd29975c</t>
         </is>
@@ -716,12 +722,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>d0bb7def-a7c4-4a2f-9732-b73b45553edf</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>b566c7c6-59f1-4ff1-baac-52b228e089c6</t>
         </is>
@@ -783,12 +789,12 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>fb3584b4-fee2-4c8a-b7f2-0570a3c4decb</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>e40dd47e-395f-49b7-9e5f-587177a03a5b</t>
         </is>
@@ -845,12 +851,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>354a3fa8-57b9-4015-af73-fbbd2a144a43</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -907,12 +913,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>20aa9f1d-6b31-434f-844f-26957fc46e7e</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -969,12 +975,12 @@
           <t>None</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>7e99b815-adc2-430a-a808-4fc52a37e967</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1106,20 +1112,25 @@
       </c>
       <c r="X11" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y11" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y11" s="1" t="inlineStr">
+      <c r="Z11" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z11" s="1" t="inlineStr">
+      <c r="AA11" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA11" s="1" t="inlineStr">
+      <c r="AB11" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -1201,12 +1212,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>d0fe871e-18c9-4102-9e06-22f32f605c8f</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>c11c5821-4c3f-463e-be2b-2fe0f436c97c</t>
         </is>
@@ -1288,12 +1299,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>674e3d93-9ee5-4919-b35a-b1c83d76dc6e</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>a3401954-773f-4825-8eaf-a22cec827dc0</t>
         </is>
@@ -1375,12 +1386,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>05c32df4-01bb-49fc-9205-1f7f050642e3</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>14a306e2-6930-4123-8a70-7458136f2de7</t>
         </is>
@@ -1462,12 +1473,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>5805cedf-1e3d-4200-959d-14681339d814</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>f1b205dc-dc35-4eeb-8f87-f1ceb2f80e98</t>
         </is>
@@ -1549,12 +1560,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>e12fd11a-c56d-4f8e-823e-e3415f2dc8db</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>da5ac7b5-d459-4093-ae5d-43a0af5acc59</t>
         </is>
@@ -1636,12 +1647,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>16fa1c05-b4c3-4ac8-bd5e-2bf5e07409a7</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>01b1050c-7f6b-4569-ac17-a37a4b2f9d1c</t>
         </is>
@@ -1723,12 +1734,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>7bbbc0af-c995-4462-a8ac-fd8090aa63c6</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>26faffbd-20b8-4ae8-bccd-d7f4e8e4b3d0</t>
         </is>
@@ -1810,12 +1821,12 @@
           <t>h</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>6abafbd3-ee44-4320-a370-41bd29a6de78</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>e165a4b8-0ee9-4ed9-9b03-dc0e1552eb32</t>
         </is>
@@ -1897,12 +1908,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>aa22816d-44a0-4da2-89de-1fd0b4690539</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>fda984c7-c4e9-43b0-833e-1df38c01f81a</t>
         </is>
@@ -1984,12 +1995,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>b73664f8-45e7-448c-93a3-467ae5656d8a</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>589047a7-bc16-4f78-be4d-cd16ec3cbae3</t>
         </is>
@@ -2071,12 +2082,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>265b4dce-fafd-4275-8218-d1dda4491014</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>214d9cf9-e7bc-4dfc-b2b7-56e4c7f1e249</t>
         </is>
@@ -2158,12 +2169,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>1a5ee9d1-1442-47aa-ab41-be1015288aea</t>
         </is>
       </c>
-      <c r="Y23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>597d26df-635a-4eee-8e48-e7b26a4fc9a2</t>
         </is>
@@ -2245,12 +2256,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>3b123a37-3d2f-498c-8c10-da11272ac272</t>
         </is>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>b0253891-754f-42e5-ae64-02b0d48081a3</t>
         </is>
@@ -2332,12 +2343,12 @@
           <t>s</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>55247c71-423f-42ce-8b00-203110f45123</t>
         </is>
       </c>
-      <c r="Y25" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>5a252edc-601b-4730-b528-e3f670c0acf0</t>
         </is>
@@ -2419,12 +2430,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>21ae6adc-9c63-40ac-84f4-6e8dff23dd48</t>
         </is>
       </c>
-      <c r="Y26" t="inlineStr">
+      <c r="Z26" t="inlineStr">
         <is>
           <t>43c0db2b-89ea-4b3e-a59f-1aac18ffbb22</t>
         </is>
@@ -2506,12 +2517,12 @@
           <t>l</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>ac0c4155-d470-45dc-9595-dcec3ba378d9</t>
         </is>
       </c>
-      <c r="Y27" t="inlineStr">
+      <c r="Z27" t="inlineStr">
         <is>
           <t>e33214dc-55d6-4479-a7ea-387b3f76d326</t>
         </is>
@@ -2593,12 +2604,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>1d539d61-0b7b-4e22-87b1-e2d4100c8abb</t>
         </is>
       </c>
-      <c r="Y28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>4c84e01c-12b9-4b41-95cc-020af95f5324</t>
         </is>
@@ -2680,12 +2691,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>11c7267a-c39d-49c1-b959-42123ff1ce22</t>
         </is>
       </c>
-      <c r="Y29" t="inlineStr">
+      <c r="Z29" t="inlineStr">
         <is>
           <t>455d4522-789d-400b-8758-e6af7b8a035a</t>
         </is>
@@ -2767,12 +2778,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>31b0a3bf-b218-4359-b3a7-6a38a8e8f4a6</t>
         </is>
       </c>
-      <c r="Y30" t="inlineStr">
+      <c r="Z30" t="inlineStr">
         <is>
           <t>68e2a749-306c-4503-95e1-714cc74a9164</t>
         </is>
@@ -2854,12 +2865,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>c62f6e25-f1f9-41e7-9e4c-95fda009ffe1</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Z31" t="inlineStr">
         <is>
           <t>28592cc0-881a-4ab6-a271-b773b79bc67a</t>
         </is>
@@ -2941,12 +2952,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>4590ff13-31f5-4e74-a583-c6a8fb6f887c</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="Z32" t="inlineStr">
         <is>
           <t>c9edf025-bf07-4760-bbdd-4708f44c70d3</t>
         </is>
@@ -3028,12 +3039,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>e383c99b-dde3-411d-9379-55338285d041</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>38a33913-5fe4-4a29-8e7d-ebd8c1b5db4c</t>
         </is>
@@ -3115,12 +3126,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>54e53605-c2e3-4307-97c4-95f9e1c48af6</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>303b8b8e-933a-40cb-a937-eafb31ac8e8c</t>
         </is>
@@ -3202,12 +3213,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>76071afc-dbb9-4c02-b87f-3ac9712044f0</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="Z35" t="inlineStr">
         <is>
           <t>5e1280f2-b4c1-441f-aef0-eadfbe30a6cc</t>
         </is>
@@ -3339,20 +3350,25 @@
       </c>
       <c r="X38" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y38" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y38" s="1" t="inlineStr">
+      <c r="Z38" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z38" s="1" t="inlineStr">
+      <c r="AA38" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA38" s="1" t="inlineStr">
+      <c r="AB38" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -3404,12 +3420,12 @@
           <t>hm</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
+      <c r="Y39" t="inlineStr">
         <is>
           <t>0916750b-3abb-44b3-8382-0e42e5e483d3</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr">
+      <c r="Z39" t="inlineStr">
         <is>
           <t>b4415182-0fe4-4f17-9de0-a9c777664077</t>
         </is>
@@ -3501,12 +3517,12 @@
           <t>hmm</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
+      <c r="Y40" t="inlineStr">
         <is>
           <t>8e02f0e7-2fff-45e4-9901-078edd411a2b</t>
         </is>
       </c>
-      <c r="Y40" t="inlineStr">
+      <c r="Z40" t="inlineStr">
         <is>
           <t>8ef73924-b280-4476-ac1a-785100cac970</t>
         </is>
@@ -3603,12 +3619,12 @@
           <t>On the last spin Yoshimitsu will be dizzy and fall over.</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>b6cc6390-1e96-45e3-9660-b51a84f00db3</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr">
+      <c r="Z41" t="inlineStr">
         <is>
           <t>2528258e-f785-4254-b6c3-b4ae0df42b49</t>
         </is>
@@ -3700,17 +3716,17 @@
           <t>Can be done after any number of Spins but the last.; Yoshimitsu receives damage.</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="Y42" t="inlineStr">
         <is>
           <t>bf02113c-50b8-4d08-9f98-d2d87caa2f36</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
+      <c r="Z42" t="inlineStr">
         <is>
           <t>bfc31ad9-932d-48f0-9c24-5dae165237cd</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
+      <c r="AA42" t="inlineStr">
         <is>
           <t>b6cc6390-1e96-45e3-9660-b51a84f00db3</t>
         </is>
@@ -3807,12 +3823,12 @@
           <t>JGc GB ST</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
+      <c r="Y43" t="inlineStr">
         <is>
           <t>733167f4-4aad-45fa-b396-cf733784a8fc</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>fefd2f24-515a-405d-82ea-b53b4c78b6dc</t>
         </is>
@@ -3909,12 +3925,12 @@
           <t>OB</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="Y44" t="inlineStr">
         <is>
           <t>73ba3127-1729-4214-976c-352867fcac3e</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>2362d783-ff3b-4228-96d2-a297ba6015f0</t>
         </is>
@@ -4011,17 +4027,17 @@
           <t>On the last spin Yoshimitsu will be dizzy and fall over.</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="Y45" t="inlineStr">
         <is>
           <t>e022df41-3ac8-4138-92e5-3afaabd346b4</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr">
+      <c r="Z45" t="inlineStr">
         <is>
           <t>d9209ca4-dfa0-410a-a7e2-212881ef4d15</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
+      <c r="AA45" t="inlineStr">
         <is>
           <t>73ba3127-1729-4214-976c-352867fcac3e</t>
         </is>
@@ -4113,12 +4129,12 @@
           <t>mhhm</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="Y46" t="inlineStr">
         <is>
           <t>13bb4439-83e9-42c6-af67-73cb7e8541a9</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr">
+      <c r="Z46" t="inlineStr">
         <is>
           <t>ac91a546-b44e-4806-8356-239bf2319d29</t>
         </is>
@@ -4210,12 +4226,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="Y47" t="inlineStr">
         <is>
           <t>85a0bb1c-31f5-4d6f-8e61-24ae9bccae1b</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr">
+      <c r="Z47" t="inlineStr">
         <is>
           <t>0bcec053-9917-4909-9825-a5a92e49a567</t>
         </is>
@@ -4312,12 +4328,12 @@
           <t>BK</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
+      <c r="Y48" t="inlineStr">
         <is>
           <t>0e4128be-4241-4e14-83b4-9d1adbf71beb</t>
         </is>
       </c>
-      <c r="Y48" t="inlineStr">
+      <c r="Z48" t="inlineStr">
         <is>
           <t>3bb150d9-ae48-46c0-8c6a-b3e7b35d3aba</t>
         </is>
@@ -4399,17 +4415,17 @@
           <t>Yoshimitsu regains energy.</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
+      <c r="Y49" t="inlineStr">
         <is>
           <t>a8eadfae-17d2-48aa-90f2-d5c730550ae3</t>
         </is>
       </c>
-      <c r="Y49" t="inlineStr">
+      <c r="Z49" t="inlineStr">
         <is>
           <t>53f42ff4-d7f3-4641-bd64-b424c059dbfa</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
+      <c r="AA49" t="inlineStr">
         <is>
           <t>0e4128be-4241-4e14-83b4-9d1adbf71beb</t>
         </is>
@@ -4491,17 +4507,17 @@
           <t>Yoshimitsu receives damage.</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
+      <c r="Y50" t="inlineStr">
         <is>
           <t>5f0bc975-4c5c-4e6d-af58-ddbc5ae2243e</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr">
+      <c r="Z50" t="inlineStr">
         <is>
           <t>7c956afc-8402-460d-bf2b-b2831c79fcdb</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
+      <c r="AA50" t="inlineStr">
         <is>
           <t>0e4128be-4241-4e14-83b4-9d1adbf71beb</t>
         </is>
@@ -4603,12 +4619,12 @@
           <t>On the last spin Yoshimitsu will be dizzy and fall over.</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
+      <c r="Y51" t="inlineStr">
         <is>
           <t>210f482c-84b7-40aa-ba46-4f3203512d6f</t>
         </is>
       </c>
-      <c r="Y51" t="inlineStr">
+      <c r="Z51" t="inlineStr">
         <is>
           <t>9e777cea-49ea-441c-860c-9b6e279065bb</t>
         </is>
@@ -4700,12 +4716,12 @@
           <t>hh</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
+      <c r="Y52" t="inlineStr">
         <is>
           <t>fdafd446-54c6-4b76-a9ee-a10d57cf3d39</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>6d4160db-e37b-4554-9c23-2d050f5cf704</t>
         </is>
@@ -4802,12 +4818,12 @@
           <t>RC</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
+      <c r="Y53" t="inlineStr">
         <is>
           <t>5f864233-8a86-40c8-88ee-dc1ca31d6dbd</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr">
+      <c r="Z53" t="inlineStr">
         <is>
           <t>4ca114bc-3499-465d-9412-8fb5ca96424f</t>
         </is>
@@ -4816,22 +4832,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SS+2 [~5]</t>
+          <t>SS+2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SS+2 [~5]</t>
+          <t>SS+2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Shrine Lift - [Tag]</t>
+          <t>Shrine Lift -</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Shrine Lift - [Tag]</t>
+          <t>Shrine Lift -</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -4906,10 +4922,15 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
           <t>5d948d81-ba78-4caf-8c85-10153ff6d3ef</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t>bc48b936-b6fb-4cfd-b85d-eef873bd7026</t>
         </is>
@@ -5006,12 +5027,12 @@
           <t>OB</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
+      <c r="Y55" t="inlineStr">
         <is>
           <t>01d76bf1-3e8f-490a-b9ef-6b00e5469861</t>
         </is>
       </c>
-      <c r="Y55" t="inlineStr">
+      <c r="Z55" t="inlineStr">
         <is>
           <t>3d98555e-1218-4907-a434-df5400d5b488</t>
         </is>
@@ -5108,17 +5129,17 @@
           <t>On the last spin Yoshimitsu will be dizzy and fall over.</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
+      <c r="Y56" t="inlineStr">
         <is>
           <t>d4d66a31-f374-4bcf-a1aa-05bca47fc136</t>
         </is>
       </c>
-      <c r="Y56" t="inlineStr">
+      <c r="Z56" t="inlineStr">
         <is>
           <t>3aa26636-6386-4d39-8132-ff88b1c69526</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
+      <c r="AA56" t="inlineStr">
         <is>
           <t>01d76bf1-3e8f-490a-b9ef-6b00e5469861</t>
         </is>
@@ -5210,12 +5231,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
+      <c r="Y57" t="inlineStr">
         <is>
           <t>85bfb5bd-4958-42e9-9617-9d5e4fa01221</t>
         </is>
       </c>
-      <c r="Y57" t="inlineStr">
+      <c r="Z57" t="inlineStr">
         <is>
           <t>7ece36f1-b397-42ce-a784-bd6718f3ce05</t>
         </is>
@@ -5272,12 +5293,12 @@
           <t>CH</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
+      <c r="Y58" t="inlineStr">
         <is>
           <t>1f4b7340-b3de-40ae-abd1-0928690a8516</t>
         </is>
       </c>
-      <c r="Y58" t="inlineStr">
+      <c r="Z58" t="inlineStr">
         <is>
           <t>a03f89b3-bb28-449c-a786-f6c34877c37f</t>
         </is>
@@ -5334,17 +5355,17 @@
           <t>Will cause the move to do less damage. Inputting a direction after the move will also cause the move to do less damage.</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
+      <c r="Y59" t="inlineStr">
         <is>
           <t>7dd15930-c164-4b8d-9a38-151474aa41d7</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr">
+      <c r="Z59" t="inlineStr">
         <is>
           <t>1461690f-5165-4d39-8bfb-cf48ef9d1266</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
+      <c r="AA59" t="inlineStr">
         <is>
           <t>1f4b7340-b3de-40ae-abd1-0928690a8516</t>
         </is>
@@ -5353,22 +5374,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>df+2 [~5]</t>
+          <t>df+2</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>df+2 [~5]</t>
+          <t>df+2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Step in Upper [Tag]</t>
+          <t>Step in Upper</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Step in Upper [Tag]</t>
+          <t>Step in Upper</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5443,10 +5464,15 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
           <t>f2c4ee40-c680-4be8-93fb-56a7fa524f13</t>
         </is>
       </c>
-      <c r="Y60" t="inlineStr">
+      <c r="Z60" t="inlineStr">
         <is>
           <t>3c385523-f722-4fff-ac31-2fafd821c900</t>
         </is>
@@ -5543,12 +5569,12 @@
           <t>JG BS</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
+      <c r="Y61" t="inlineStr">
         <is>
           <t>825ac877-9126-442c-9cf6-ce6252008059</t>
         </is>
       </c>
-      <c r="Y61" t="inlineStr">
+      <c r="Z61" t="inlineStr">
         <is>
           <t>70e6870e-3088-4f08-b526-4b596d7ee2b6</t>
         </is>
@@ -5650,12 +5676,12 @@
           <t>On the last spin Yoshimitsu will be dizzy and fall over.</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
+      <c r="Y62" t="inlineStr">
         <is>
           <t>743c1955-56e8-4297-9384-151bbda0ad01</t>
         </is>
       </c>
-      <c r="Y62" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t>05a24c1e-6d0d-40b3-9bac-1eab0027c1ca</t>
         </is>
@@ -5732,17 +5758,17 @@
           <t>Lllllm</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
+      <c r="Y63" t="inlineStr">
         <is>
           <t>82eeffa1-22fa-4037-b62d-abdfe5a96166</t>
         </is>
       </c>
-      <c r="Y63" t="inlineStr">
+      <c r="Z63" t="inlineStr">
         <is>
           <t>43a485b5-21be-4bd8-ad1b-68ba48b90838</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
+      <c r="AA63" t="inlineStr">
         <is>
           <t>743c1955-56e8-4297-9384-151bbda0ad01</t>
         </is>
@@ -5834,12 +5860,12 @@
           <t>hm</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
+      <c r="Y64" t="inlineStr">
         <is>
           <t>d38482d3-8aed-4ee1-862a-7f60baeefdc9</t>
         </is>
       </c>
-      <c r="Y64" t="inlineStr">
+      <c r="Z64" t="inlineStr">
         <is>
           <t>42c1ad13-6d89-43ac-bcd9-05e720126151</t>
         </is>
@@ -5848,22 +5874,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3,df+3+4 [~5]</t>
+          <t>3,df+3+4</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>3,df+3+4 [~5]</t>
+          <t>3,df+3+4</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Zig Kangaroo Kick [Tag]</t>
+          <t>Zig Kangaroo Kick</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Zig Kangaroo Kick [Tag]</t>
+          <t>Zig Kangaroo Kick</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5938,10 +5964,15 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
           <t>ef2098dc-ac05-456f-a11f-6411f852168a</t>
         </is>
       </c>
-      <c r="Y65" t="inlineStr">
+      <c r="Z65" t="inlineStr">
         <is>
           <t>042e464e-29ff-42b7-9305-9190c8677030</t>
         </is>
@@ -6033,12 +6064,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
+      <c r="Y66" t="inlineStr">
         <is>
           <t>95076e5c-754c-436b-a680-4399bd882567</t>
         </is>
       </c>
-      <c r="Y66" t="inlineStr">
+      <c r="Z66" t="inlineStr">
         <is>
           <t>03875693-ff9e-460c-9ad5-c556d4dfad92</t>
         </is>
@@ -6125,17 +6156,17 @@
           <t>mm</t>
         </is>
       </c>
-      <c r="X67" t="inlineStr">
+      <c r="Y67" t="inlineStr">
         <is>
           <t>0279f0a6-4266-40c9-8014-0bc0e81cb2e6</t>
         </is>
       </c>
-      <c r="Y67" t="inlineStr">
+      <c r="Z67" t="inlineStr">
         <is>
           <t>677f8827-de34-42b3-b7d5-0a3ef06f6e0a</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
+      <c r="AA67" t="inlineStr">
         <is>
           <t>95076e5c-754c-436b-a680-4399bd882567</t>
         </is>
@@ -6144,22 +6175,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>–– 3+4 [~5]</t>
+          <t>–– 3+4</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>f,f+3+4,1+2,3+4 [~5]</t>
+          <t>f,f+3+4,1+2,3+4</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>–– Kangaroo Kick [Tag]</t>
+          <t>–– Kangaroo Kick</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Shark Attack – Dive Bomb – Kangaroo Kick [Tag]</t>
+          <t>Shark Attack – Dive Bomb – Kangaroo Kick</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6229,15 +6260,20 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
           <t>439fab68-b1b3-4bdd-b320-bf24c3101302</t>
         </is>
       </c>
-      <c r="Y68" t="inlineStr">
+      <c r="Z68" t="inlineStr">
         <is>
           <t>6cde4901-fe63-4f31-85f3-2671db0be4ba</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
+      <c r="AA68" t="inlineStr">
         <is>
           <t>0279f0a6-4266-40c9-8014-0bc0e81cb2e6</t>
         </is>
@@ -6289,12 +6325,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
+      <c r="Y69" t="inlineStr">
         <is>
           <t>c289cbd6-4043-4691-ba77-10f44be2d55a</t>
         </is>
       </c>
-      <c r="Y69" t="inlineStr">
+      <c r="Z69" t="inlineStr">
         <is>
           <t>b071aedd-8677-474b-a77f-52e68e5e5a57</t>
         </is>
@@ -6346,17 +6382,17 @@
           <t>--</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
+      <c r="Y70" t="inlineStr">
         <is>
           <t>3007e1c3-ab9b-4cf5-853d-54701c57c927</t>
         </is>
       </c>
-      <c r="Y70" t="inlineStr">
+      <c r="Z70" t="inlineStr">
         <is>
           <t>6c6e1c24-1fef-44bc-b8de-19f48e5e5ddd</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
+      <c r="AA70" t="inlineStr">
         <is>
           <t>c289cbd6-4043-4691-ba77-10f44be2d55a</t>
         </is>
@@ -6413,17 +6449,17 @@
           <t>Close range causes a behind the opponent teleport, 3 or more characters away Yoshimitsu will be BT in the same spot.</t>
         </is>
       </c>
-      <c r="X71" t="inlineStr">
+      <c r="Y71" t="inlineStr">
         <is>
           <t>f75840c1-9a8a-4095-a7a1-3d6cae4eb3f1</t>
         </is>
       </c>
-      <c r="Y71" t="inlineStr">
+      <c r="Z71" t="inlineStr">
         <is>
           <t>5669e323-aa58-49d9-838f-1bf790066ad9</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
+      <c r="AA71" t="inlineStr">
         <is>
           <t>c289cbd6-4043-4691-ba77-10f44be2d55a</t>
         </is>
@@ -6475,17 +6511,17 @@
           <t>--</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
+      <c r="Y72" t="inlineStr">
         <is>
           <t>7e2df490-93d5-4090-b469-c1d8c301b495</t>
         </is>
       </c>
-      <c r="Y72" t="inlineStr">
+      <c r="Z72" t="inlineStr">
         <is>
           <t>3efdbbe0-6d24-40d7-aecd-686c73cea9f9</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
+      <c r="AA72" t="inlineStr">
         <is>
           <t>c289cbd6-4043-4691-ba77-10f44be2d55a</t>
         </is>
@@ -6494,22 +6530,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>– 4 [~5]</t>
+          <t>– 4</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>d+3+4,4 [~5]</t>
+          <t>d+3+4,4</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>– Kangaroo Kick [Tag]</t>
+          <t>– Kangaroo Kick</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Indian Sit – Kangaroo Kick [Tag]</t>
+          <t>Indian Sit – Kangaroo Kick</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -6579,15 +6615,20 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
           <t>e7749750-4041-4d70-8150-e8513accf95e</t>
         </is>
       </c>
-      <c r="Y73" t="inlineStr">
+      <c r="Z73" t="inlineStr">
         <is>
           <t>e5279897-78cb-4307-a48c-1111d74b73d1</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
+      <c r="AA73" t="inlineStr">
         <is>
           <t>c289cbd6-4043-4691-ba77-10f44be2d55a</t>
         </is>
@@ -6679,17 +6720,17 @@
           <t>On the last spin Yoshimitsu will be dizzy and fall over.</t>
         </is>
       </c>
-      <c r="X74" t="inlineStr">
+      <c r="Y74" t="inlineStr">
         <is>
           <t>5177f1dd-7a1a-4bcf-8558-21725db7af1d</t>
         </is>
       </c>
-      <c r="Y74" t="inlineStr">
+      <c r="Z74" t="inlineStr">
         <is>
           <t>74d9c87d-2394-4b1a-aa77-e8b5b84e3052</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
+      <c r="AA74" t="inlineStr">
         <is>
           <t>c289cbd6-4043-4691-ba77-10f44be2d55a</t>
         </is>
@@ -6741,12 +6782,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X75" t="inlineStr">
+      <c r="Y75" t="inlineStr">
         <is>
           <t>0758833c-cc26-446e-9760-16ef52204468</t>
         </is>
       </c>
-      <c r="Y75" t="inlineStr">
+      <c r="Z75" t="inlineStr">
         <is>
           <t>2a2f1d55-8d7b-4fa7-957d-487d53862a46</t>
         </is>
@@ -6808,17 +6849,17 @@
           <t>Yoshimitsu regains energy.</t>
         </is>
       </c>
-      <c r="X76" t="inlineStr">
+      <c r="Y76" t="inlineStr">
         <is>
           <t>cd75d332-0bfa-45a2-8077-8161afcacf98</t>
         </is>
       </c>
-      <c r="Y76" t="inlineStr">
+      <c r="Z76" t="inlineStr">
         <is>
           <t>a434b577-99c0-4ca6-8a2c-24eddac64c53</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
+      <c r="AA76" t="inlineStr">
         <is>
           <t>0758833c-cc26-446e-9760-16ef52204468</t>
         </is>
@@ -6880,17 +6921,17 @@
           <t>Yoshimitsu receives damage.</t>
         </is>
       </c>
-      <c r="X77" t="inlineStr">
+      <c r="Y77" t="inlineStr">
         <is>
           <t>4643d426-7153-420e-8ca6-638df281c868</t>
         </is>
       </c>
-      <c r="Y77" t="inlineStr">
+      <c r="Z77" t="inlineStr">
         <is>
           <t>2bc08d04-dda4-43be-816a-78dc0c0fa03a</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
+      <c r="AA77" t="inlineStr">
         <is>
           <t>0758833c-cc26-446e-9760-16ef52204468</t>
         </is>
@@ -6982,12 +7023,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X78" t="inlineStr">
+      <c r="Y78" t="inlineStr">
         <is>
           <t>b6cc27c7-4533-40d4-9105-aeb9014c943e</t>
         </is>
       </c>
-      <c r="Y78" t="inlineStr">
+      <c r="Z78" t="inlineStr">
         <is>
           <t>6cb29627-0dfd-45f3-b6a7-22c74de9b370</t>
         </is>
@@ -6996,22 +7037,22 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>– 3+4 [~5]</t>
+          <t>– 3+4</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>uf+3+4,3+4 [~5]</t>
+          <t>uf+3+4,3+4</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>– Kangaroo Kick [Tag]</t>
+          <t>– Kangaroo Kick</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Poison Wind – Kangaroo Kick [Tag]</t>
+          <t>Poison Wind – Kangaroo Kick</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -7081,15 +7122,20 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
           <t>ac9ace2d-f03d-4b00-8e9f-629fa7ad7017</t>
         </is>
       </c>
-      <c r="Y79" t="inlineStr">
+      <c r="Z79" t="inlineStr">
         <is>
           <t>00b575ca-7589-4513-94c5-0feb4f2c689c</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
+      <c r="AA79" t="inlineStr">
         <is>
           <t>b6cc27c7-4533-40d4-9105-aeb9014c943e</t>
         </is>
@@ -7176,17 +7222,17 @@
           <t>ms</t>
         </is>
       </c>
-      <c r="X80" t="inlineStr">
+      <c r="Y80" t="inlineStr">
         <is>
           <t>e7f874a0-81cd-4de6-9f52-934cf05c555a</t>
         </is>
       </c>
-      <c r="Y80" t="inlineStr">
+      <c r="Z80" t="inlineStr">
         <is>
           <t>f4454657-f0dd-4a67-991b-c6c1ca52a1f3</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
+      <c r="AA80" t="inlineStr">
         <is>
           <t>b6cc27c7-4533-40d4-9105-aeb9014c943e</t>
         </is>
@@ -7273,17 +7319,17 @@
           <t>msm</t>
         </is>
       </c>
-      <c r="X81" t="inlineStr">
+      <c r="Y81" t="inlineStr">
         <is>
           <t>b42aa201-9586-405d-a2fb-a6616841fdba</t>
         </is>
       </c>
-      <c r="Y81" t="inlineStr">
+      <c r="Z81" t="inlineStr">
         <is>
           <t>2e3ea01d-a63b-4884-8be6-e914a42733f6</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
+      <c r="AA81" t="inlineStr">
         <is>
           <t>e7f874a0-81cd-4de6-9f52-934cf05c555a</t>
         </is>
@@ -7370,17 +7416,17 @@
           <t>mss</t>
         </is>
       </c>
-      <c r="X82" t="inlineStr">
+      <c r="Y82" t="inlineStr">
         <is>
           <t>a8df444d-4004-4b71-9d7d-330f5da27c92</t>
         </is>
       </c>
-      <c r="Y82" t="inlineStr">
+      <c r="Z82" t="inlineStr">
         <is>
           <t>94b31900-f97d-48c4-a5ae-7f6eafda2aad</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
+      <c r="AA82" t="inlineStr">
         <is>
           <t>e7f874a0-81cd-4de6-9f52-934cf05c555a</t>
         </is>
@@ -7452,17 +7498,17 @@
           <t>ms[!]</t>
         </is>
       </c>
-      <c r="X83" t="inlineStr">
+      <c r="Y83" t="inlineStr">
         <is>
           <t>e5efaf28-51d0-43a5-acfe-f65b024d0d47</t>
         </is>
       </c>
-      <c r="Y83" t="inlineStr">
+      <c r="Z83" t="inlineStr">
         <is>
           <t>397a9b4d-3a0b-43cb-a805-c5fd75562f16</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
+      <c r="AA83" t="inlineStr">
         <is>
           <t>e7f874a0-81cd-4de6-9f52-934cf05c555a</t>
         </is>
@@ -7514,12 +7560,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X84" t="inlineStr">
+      <c r="Y84" t="inlineStr">
         <is>
           <t>17316f4e-fead-4f30-adfe-f1188ed257c3</t>
         </is>
       </c>
-      <c r="Y84" t="inlineStr">
+      <c r="Z84" t="inlineStr">
         <is>
           <t>41b68c67-8440-4cc7-9e83-b01f76de0cff</t>
         </is>
@@ -7571,17 +7617,17 @@
           <t>--</t>
         </is>
       </c>
-      <c r="X85" t="inlineStr">
+      <c r="Y85" t="inlineStr">
         <is>
           <t>5def0b25-95c2-4571-851d-c798470b2e06</t>
         </is>
       </c>
-      <c r="Y85" t="inlineStr">
+      <c r="Z85" t="inlineStr">
         <is>
           <t>2155ff6c-8ec8-4656-8ec2-776d06af6da7</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
+      <c r="AA85" t="inlineStr">
         <is>
           <t>17316f4e-fead-4f30-adfe-f1188ed257c3</t>
         </is>
@@ -7638,17 +7684,17 @@
           <t>Close range causes a behind the opponent teleport, 3 or more characters away Yoshimitsu will be BT in the same spot.</t>
         </is>
       </c>
-      <c r="X86" t="inlineStr">
+      <c r="Y86" t="inlineStr">
         <is>
           <t>5d15674d-e708-44fb-9a21-62664493df41</t>
         </is>
       </c>
-      <c r="Y86" t="inlineStr">
+      <c r="Z86" t="inlineStr">
         <is>
           <t>62369940-f435-4304-90ad-c5d18de0343f</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
+      <c r="AA86" t="inlineStr">
         <is>
           <t>17316f4e-fead-4f30-adfe-f1188ed257c3</t>
         </is>
@@ -7705,17 +7751,17 @@
           <t>Yoshimitsu regains energy.</t>
         </is>
       </c>
-      <c r="X87" t="inlineStr">
+      <c r="Y87" t="inlineStr">
         <is>
           <t>026fecd9-7969-45b8-97d8-5012e0e94827</t>
         </is>
       </c>
-      <c r="Y87" t="inlineStr">
+      <c r="Z87" t="inlineStr">
         <is>
           <t>ef7c5d29-ddf7-427f-ac04-4c0ae24ae697</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
+      <c r="AA87" t="inlineStr">
         <is>
           <t>17316f4e-fead-4f30-adfe-f1188ed257c3</t>
         </is>
@@ -7724,22 +7770,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>– 4 [~5]</t>
+          <t>– 4</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>KND 3+4,4 [~5]</t>
+          <t>KND 3+4,4</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>– Kangaroo Kick [Tag]</t>
+          <t>– Kangaroo Kick</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Indian Sit – Kangaroo Kick [Tag]</t>
+          <t>Indian Sit – Kangaroo Kick</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -7809,15 +7855,20 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
           <t>0ceb6b92-a267-4dfb-a020-1250aab9c480</t>
         </is>
       </c>
-      <c r="Y88" t="inlineStr">
+      <c r="Z88" t="inlineStr">
         <is>
           <t>b29288bd-972f-48a8-8991-c5339ec26ee9</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
+      <c r="AA88" t="inlineStr">
         <is>
           <t>17316f4e-fead-4f30-adfe-f1188ed257c3</t>
         </is>
@@ -7909,17 +7960,17 @@
           <t>On the last spin Yoshimitsu will be dizzy and fall over.</t>
         </is>
       </c>
-      <c r="X89" t="inlineStr">
+      <c r="Y89" t="inlineStr">
         <is>
           <t>fccd2ecf-8d1f-49bb-8a54-7be22e4c87a6</t>
         </is>
       </c>
-      <c r="Y89" t="inlineStr">
+      <c r="Z89" t="inlineStr">
         <is>
           <t>7ebfcc75-63aa-4d10-986f-7ee6b26d0cc4</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
+      <c r="AA89" t="inlineStr">
         <is>
           <t>17316f4e-fead-4f30-adfe-f1188ed257c3</t>
         </is>
@@ -8011,12 +8062,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X90" t="inlineStr">
+      <c r="Y90" t="inlineStr">
         <is>
           <t>e5204595-04ad-41d6-88f3-8270b9ce7485</t>
         </is>
       </c>
-      <c r="Y90" t="inlineStr">
+      <c r="Z90" t="inlineStr">
         <is>
           <t>2b414595-7286-4379-a2bc-50476e5e2f9a</t>
         </is>
@@ -8113,12 +8164,12 @@
           <t>CSc</t>
         </is>
       </c>
-      <c r="X91" t="inlineStr">
+      <c r="Y91" t="inlineStr">
         <is>
           <t>ebcb244b-6a1e-413a-8e18-594d5c4f4504</t>
         </is>
       </c>
-      <c r="Y91" t="inlineStr">
+      <c r="Z91" t="inlineStr">
         <is>
           <t>378a7c75-d5e0-4045-902d-1ce451d7a07e</t>
         </is>
@@ -8210,12 +8261,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X92" t="inlineStr">
+      <c r="Y92" t="inlineStr">
         <is>
           <t>56fa2660-e1e5-4e1d-95d2-4e9a746a4e93</t>
         </is>
       </c>
-      <c r="Y92" t="inlineStr">
+      <c r="Z92" t="inlineStr">
         <is>
           <t>45b400ac-c2d1-43ed-88bd-e8c99413b73b</t>
         </is>
@@ -8312,12 +8363,12 @@
           <t>OB</t>
         </is>
       </c>
-      <c r="X93" t="inlineStr">
+      <c r="Y93" t="inlineStr">
         <is>
           <t>80cb90af-3c19-4f4f-b4d4-cc1dab97febc</t>
         </is>
       </c>
-      <c r="Y93" t="inlineStr">
+      <c r="Z93" t="inlineStr">
         <is>
           <t>bbe21903-f1ae-4f6c-9d3f-e46538a28fa5</t>
         </is>
@@ -8326,22 +8377,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>4~3 [~5]</t>
+          <t>4~3</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>4~3 [~5]</t>
+          <t>4~3</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Kangaroo Kick [Tag]</t>
+          <t>Kangaroo Kick</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Kangaroo Kick [Tag]</t>
+          <t>Kangaroo Kick</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -8416,10 +8467,15 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
           <t>466af155-ff3e-4e08-8485-677bee9a5053</t>
         </is>
       </c>
-      <c r="Y94" t="inlineStr">
+      <c r="Z94" t="inlineStr">
         <is>
           <t>8cc09155-b86b-46f1-b1f8-d67845b7fc0b</t>
         </is>
@@ -8516,12 +8572,12 @@
           <t>m</t>
         </is>
       </c>
-      <c r="X95" t="inlineStr">
+      <c r="Y95" t="inlineStr">
         <is>
           <t>78bbcd9f-9107-44ee-ac32-399787a9d23f</t>
         </is>
       </c>
-      <c r="Y95" t="inlineStr">
+      <c r="Z95" t="inlineStr">
         <is>
           <t>0e12c14f-62c1-4028-93f4-581e31636837</t>
         </is>
@@ -8578,12 +8634,12 @@
           <t>BK</t>
         </is>
       </c>
-      <c r="X96" t="inlineStr">
+      <c r="Y96" t="inlineStr">
         <is>
           <t>ded0ad69-65c3-4298-a0a2-680033ee690b</t>
         </is>
       </c>
-      <c r="Y96" t="inlineStr">
+      <c r="Z96" t="inlineStr">
         <is>
           <t>6cf4a4d6-1646-44f4-a324-f6df08a31f5f</t>
         </is>
@@ -8680,12 +8736,12 @@
           <t>Repels all attacks.</t>
         </is>
       </c>
-      <c r="X97" t="inlineStr">
+      <c r="Y97" t="inlineStr">
         <is>
           <t>d2a5bb84-9907-4b1d-85a4-28259ea02c25</t>
         </is>
       </c>
-      <c r="Y97" t="inlineStr">
+      <c r="Z97" t="inlineStr">
         <is>
           <t>3911a6f3-b837-4ddb-99c6-17a38798a51e</t>
         </is>
@@ -8737,12 +8793,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X98" t="inlineStr">
+      <c r="Y98" t="inlineStr">
         <is>
           <t>93eecde9-fd5e-4b75-bbd1-f989e366709e</t>
         </is>
       </c>
-      <c r="Y98" t="inlineStr">
+      <c r="Z98" t="inlineStr">
         <is>
           <t>204dccbd-0d92-40af-8b86-7d1c2ebfc8ea</t>
         </is>
@@ -8799,12 +8855,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X99" t="inlineStr">
+      <c r="Y99" t="inlineStr">
         <is>
           <t>7c246c07-3b2b-45b5-9c83-24ac2cb50ed6</t>
         </is>
       </c>
-      <c r="Y99" t="inlineStr">
+      <c r="Z99" t="inlineStr">
         <is>
           <t>4af9f83a-1903-4311-8810-cbec45257c15</t>
         </is>
@@ -8861,12 +8917,12 @@
           <t>Yoshimitsu receives damage.</t>
         </is>
       </c>
-      <c r="X100" t="inlineStr">
+      <c r="Y100" t="inlineStr">
         <is>
           <t>8f1c24d9-bbeb-4bb3-a85b-d69e91982cef</t>
         </is>
       </c>
-      <c r="Y100" t="inlineStr">
+      <c r="Z100" t="inlineStr">
         <is>
           <t>ad8029be-7840-4843-a42f-75305af71440</t>
         </is>
@@ -8998,20 +9054,25 @@
       </c>
       <c r="X103" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y103" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y103" s="1" t="inlineStr">
+      <c r="Z103" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z103" s="1" t="inlineStr">
+      <c r="AA103" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA103" s="1" t="inlineStr">
+      <c r="AB103" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -9103,12 +9164,12 @@
           <t>!</t>
         </is>
       </c>
-      <c r="X104" t="inlineStr">
+      <c r="Y104" t="inlineStr">
         <is>
           <t>d4905cd1-2b6d-426d-9163-c5f467cb9951</t>
         </is>
       </c>
-      <c r="Y104" t="inlineStr">
+      <c r="Z104" t="inlineStr">
         <is>
           <t>45747987-7cde-4b7a-9d23-af79a25d2e73</t>
         </is>
@@ -9200,17 +9261,17 @@
           <t>!!</t>
         </is>
       </c>
-      <c r="X105" t="inlineStr">
+      <c r="Y105" t="inlineStr">
         <is>
           <t>dbdd76d0-600e-43ca-873d-df4f4839d81e</t>
         </is>
       </c>
-      <c r="Y105" t="inlineStr">
+      <c r="Z105" t="inlineStr">
         <is>
           <t>92dd4396-817c-4ca9-b00b-0a17280e297b</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
+      <c r="AA105" t="inlineStr">
         <is>
           <t>d4905cd1-2b6d-426d-9163-c5f467cb9951</t>
         </is>
@@ -9307,12 +9368,12 @@
           <t>[!]</t>
         </is>
       </c>
-      <c r="X106" t="inlineStr">
+      <c r="Y106" t="inlineStr">
         <is>
           <t>325ac655-4904-4851-b98b-46ae7f8b1fc6</t>
         </is>
       </c>
-      <c r="Y106" t="inlineStr">
+      <c r="Z106" t="inlineStr">
         <is>
           <t>5ea99dcd-a145-47fc-b1d3-3ae84773c2ea</t>
         </is>
@@ -9404,17 +9465,17 @@
           <t>[!][!]</t>
         </is>
       </c>
-      <c r="X107" t="inlineStr">
+      <c r="Y107" t="inlineStr">
         <is>
           <t>f9cfd9e6-9944-4159-b810-2e4f5d83d738</t>
         </is>
       </c>
-      <c r="Y107" t="inlineStr">
+      <c r="Z107" t="inlineStr">
         <is>
           <t>8f9879f6-3f6f-423f-b64e-d0ad3859dc76</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
+      <c r="AA107" t="inlineStr">
         <is>
           <t>325ac655-4904-4851-b98b-46ae7f8b1fc6</t>
         </is>
@@ -9506,17 +9567,17 @@
           <t>[!][!]</t>
         </is>
       </c>
-      <c r="X108" t="inlineStr">
+      <c r="Y108" t="inlineStr">
         <is>
           <t>414ecb13-0184-4bbd-b93f-1284452db915</t>
         </is>
       </c>
-      <c r="Y108" t="inlineStr">
+      <c r="Z108" t="inlineStr">
         <is>
           <t>d39864c0-6f33-450e-87c6-fa74978d2c23</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
+      <c r="AA108" t="inlineStr">
         <is>
           <t>325ac655-4904-4851-b98b-46ae7f8b1fc6</t>
         </is>
@@ -9613,17 +9674,17 @@
           <t>ST GB JGc</t>
         </is>
       </c>
-      <c r="X109" t="inlineStr">
+      <c r="Y109" t="inlineStr">
         <is>
           <t>f045e5f8-322a-4ce0-a88a-228de8560103</t>
         </is>
       </c>
-      <c r="Y109" t="inlineStr">
+      <c r="Z109" t="inlineStr">
         <is>
           <t>27031f7d-2e02-4e21-8853-73472e4bcb6c</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
+      <c r="AA109" t="inlineStr">
         <is>
           <t>325ac655-4904-4851-b98b-46ae7f8b1fc6</t>
         </is>
@@ -9700,17 +9761,17 @@
           <t>Continue with any of the Indian Sit moves.</t>
         </is>
       </c>
-      <c r="X110" t="inlineStr">
+      <c r="Y110" t="inlineStr">
         <is>
           <t>f0840bfe-9e7e-410d-9ad6-97765f5a46ff</t>
         </is>
       </c>
-      <c r="Y110" t="inlineStr">
+      <c r="Z110" t="inlineStr">
         <is>
           <t>f753c10c-001e-4fb1-af17-9b73db446896</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
+      <c r="AA110" t="inlineStr">
         <is>
           <t>325ac655-4904-4851-b98b-46ae7f8b1fc6</t>
         </is>
@@ -9719,22 +9780,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>– 3+4 [~5]</t>
+          <t>– 3+4</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1+2,3+4 [~5]</t>
+          <t>1+2,3+4</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>– Kangaroo Kick [Tag]</t>
+          <t>– Kangaroo Kick</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Flea – Kangaroo Kick [Tag]</t>
+          <t>Flea – Kangaroo Kick</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -9809,15 +9870,20 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
           <t>39eb4d93-c218-4bef-a812-6a45193d0b8b</t>
         </is>
       </c>
-      <c r="Y111" t="inlineStr">
+      <c r="Z111" t="inlineStr">
         <is>
           <t>591ce686-f0f8-4dea-99ac-01faeb4331a1</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
+      <c r="AA111" t="inlineStr">
         <is>
           <t>325ac655-4904-4851-b98b-46ae7f8b1fc6</t>
         </is>
@@ -9869,12 +9935,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X112" t="inlineStr">
+      <c r="Y112" t="inlineStr">
         <is>
           <t>0bc7647d-b937-4eb5-a181-ef48b71b3144</t>
         </is>
       </c>
-      <c r="Y112" t="inlineStr">
+      <c r="Z112" t="inlineStr">
         <is>
           <t>21d34acb-8259-4f5f-8de2-261db7f8b370</t>
         </is>
@@ -9951,17 +10017,17 @@
           <t>JG</t>
         </is>
       </c>
-      <c r="X113" t="inlineStr">
+      <c r="Y113" t="inlineStr">
         <is>
           <t>c83d86ea-8ec9-4f83-9497-3f7295388647</t>
         </is>
       </c>
-      <c r="Y113" t="inlineStr">
+      <c r="Z113" t="inlineStr">
         <is>
           <t>6b1302d5-045b-4eef-8b49-08bf9799abbc</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
+      <c r="AA113" t="inlineStr">
         <is>
           <t>0bc7647d-b937-4eb5-a181-ef48b71b3144</t>
         </is>
@@ -10023,12 +10089,12 @@
           <t>!![!]</t>
         </is>
       </c>
-      <c r="X114" t="inlineStr">
+      <c r="Y114" t="inlineStr">
         <is>
           <t>c966da6c-ca98-44d6-9274-a590a370e1de</t>
         </is>
       </c>
-      <c r="Y114" t="inlineStr">
+      <c r="Z114" t="inlineStr">
         <is>
           <t>3721d617-1e02-4ec4-a36d-1b966cde034f</t>
         </is>
@@ -10120,12 +10186,12 @@
           <t>m[!]</t>
         </is>
       </c>
-      <c r="X115" t="inlineStr">
+      <c r="Y115" t="inlineStr">
         <is>
           <t>b4753676-ac56-4327-bc11-bc1ea0fcb00a</t>
         </is>
       </c>
-      <c r="Y115" t="inlineStr">
+      <c r="Z115" t="inlineStr">
         <is>
           <t>a14d2af4-dafb-4da9-a1a4-4adb4c21c324</t>
         </is>
@@ -10207,12 +10273,12 @@
           <t>!</t>
         </is>
       </c>
-      <c r="X116" t="inlineStr">
+      <c r="Y116" t="inlineStr">
         <is>
           <t>61bd8e00-8234-4822-b730-9c00ad0a8e0e</t>
         </is>
       </c>
-      <c r="Y116" t="inlineStr">
+      <c r="Z116" t="inlineStr">
         <is>
           <t>ff2f5581-1f01-4d98-b99a-7c32d8927238</t>
         </is>
@@ -10299,12 +10365,12 @@
           <t>Yoshimitsu receives equal damage damage.</t>
         </is>
       </c>
-      <c r="X117" t="inlineStr">
+      <c r="Y117" t="inlineStr">
         <is>
           <t>ce5bef13-90ae-4c63-8972-65626344c950</t>
         </is>
       </c>
-      <c r="Y117" t="inlineStr">
+      <c r="Z117" t="inlineStr">
         <is>
           <t>2d0bbc03-f550-4968-a2f9-eb5a3ebc843f</t>
         </is>
@@ -10386,17 +10452,17 @@
           <t>Yoshimitsu receives equal damage damage.</t>
         </is>
       </c>
-      <c r="X118" t="inlineStr">
+      <c r="Y118" t="inlineStr">
         <is>
           <t>378e0bc7-91b0-4846-877d-8080c76198dc</t>
         </is>
       </c>
-      <c r="Y118" t="inlineStr">
+      <c r="Z118" t="inlineStr">
         <is>
           <t>2d3027a2-31f4-41ee-8a18-3f6fbf36f74c</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
+      <c r="AA118" t="inlineStr">
         <is>
           <t>ce5bef13-90ae-4c63-8972-65626344c950</t>
         </is>
@@ -10483,12 +10549,12 @@
           <t>Yoshimitsu receives equal damage damage.</t>
         </is>
       </c>
-      <c r="X119" t="inlineStr">
+      <c r="Y119" t="inlineStr">
         <is>
           <t>5c7e40d0-10b7-49d3-9dc4-ab79c212acbf</t>
         </is>
       </c>
-      <c r="Y119" t="inlineStr">
+      <c r="Z119" t="inlineStr">
         <is>
           <t>c7cd6ba3-2592-4338-82bc-d3e7969fbe75</t>
         </is>
@@ -10570,17 +10636,17 @@
           <t>Yoshimitsu receives equal damage damage.</t>
         </is>
       </c>
-      <c r="X120" t="inlineStr">
+      <c r="Y120" t="inlineStr">
         <is>
           <t>d360c6bf-c7c0-4abd-bd3d-8d0a4d196476</t>
         </is>
       </c>
-      <c r="Y120" t="inlineStr">
+      <c r="Z120" t="inlineStr">
         <is>
           <t>e5b16e8d-c190-4f43-aef6-0ad80ba09c51</t>
         </is>
       </c>
-      <c r="Z120" t="inlineStr">
+      <c r="AA120" t="inlineStr">
         <is>
           <t>5c7e40d0-10b7-49d3-9dc4-ab79c212acbf</t>
         </is>
@@ -10632,12 +10698,12 @@
           <t>-</t>
         </is>
       </c>
-      <c r="X121" t="inlineStr">
+      <c r="Y121" t="inlineStr">
         <is>
           <t>31fa4b69-cbce-4f67-9590-3a1093a04e99</t>
         </is>
       </c>
-      <c r="Y121" t="inlineStr">
+      <c r="Z121" t="inlineStr">
         <is>
           <t>f664b509-5372-4a16-b066-86816a8127c3</t>
         </is>
@@ -10694,17 +10760,17 @@
           <t>Yoshimitsu regains enery.</t>
         </is>
       </c>
-      <c r="X122" t="inlineStr">
+      <c r="Y122" t="inlineStr">
         <is>
           <t>02c13257-678c-4057-a052-efc413bb12bc</t>
         </is>
       </c>
-      <c r="Y122" t="inlineStr">
+      <c r="Z122" t="inlineStr">
         <is>
           <t>94028875-dbcd-4671-b762-554d00cb276f</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
+      <c r="AA122" t="inlineStr">
         <is>
           <t>31fa4b69-cbce-4f67-9590-3a1093a04e99</t>
         </is>
@@ -10786,12 +10852,12 @@
           <t>[!]</t>
         </is>
       </c>
-      <c r="X123" t="inlineStr">
+      <c r="Y123" t="inlineStr">
         <is>
           <t>a2d5e275-fd26-45a6-8ad1-05d798ab7bd0</t>
         </is>
       </c>
-      <c r="Y123" t="inlineStr">
+      <c r="Z123" t="inlineStr">
         <is>
           <t>e9ac44aa-bb98-4aa0-a97a-fe62e4fa932b</t>
         </is>
@@ -10858,17 +10924,17 @@
           <t>[!]-</t>
         </is>
       </c>
-      <c r="X124" t="inlineStr">
+      <c r="Y124" t="inlineStr">
         <is>
           <t>7eb42781-ab1d-49a5-bd79-f7051dacbca9</t>
         </is>
       </c>
-      <c r="Y124" t="inlineStr">
+      <c r="Z124" t="inlineStr">
         <is>
           <t>56fe3ad6-d9af-47cd-b017-52fbf0a8e1f8</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
+      <c r="AA124" t="inlineStr">
         <is>
           <t>a2d5e275-fd26-45a6-8ad1-05d798ab7bd0</t>
         </is>
@@ -10940,17 +11006,17 @@
           <t>Damage increases with each extra hop to 23,27,43,65,107. After the 6th hop it damage will be 15 again.</t>
         </is>
       </c>
-      <c r="X125" t="inlineStr">
+      <c r="Y125" t="inlineStr">
         <is>
           <t>56b0b30b-49cd-4b84-8cc9-47c25e72ee0c</t>
         </is>
       </c>
-      <c r="Y125" t="inlineStr">
+      <c r="Z125" t="inlineStr">
         <is>
           <t>9c72eb1d-8095-4917-b4c8-2f3f7cd57614</t>
         </is>
       </c>
-      <c r="Z125" t="inlineStr">
+      <c r="AA125" t="inlineStr">
         <is>
           <t>7eb42781-ab1d-49a5-bd79-f7051dacbca9</t>
         </is>
@@ -11032,12 +11098,12 @@
           <t>[!]</t>
         </is>
       </c>
-      <c r="X126" t="inlineStr">
+      <c r="Y126" t="inlineStr">
         <is>
           <t>a298b6ea-b0a3-4f24-9d22-7061e232a5a0</t>
         </is>
       </c>
-      <c r="Y126" t="inlineStr">
+      <c r="Z126" t="inlineStr">
         <is>
           <t>a14524b5-0954-4875-aa35-3484237b72aa</t>
         </is>
@@ -11119,17 +11185,17 @@
           <t>[!][!]</t>
         </is>
       </c>
-      <c r="X127" t="inlineStr">
+      <c r="Y127" t="inlineStr">
         <is>
           <t>92710362-a1f9-4da6-aba6-41ad8452daca</t>
         </is>
       </c>
-      <c r="Y127" t="inlineStr">
+      <c r="Z127" t="inlineStr">
         <is>
           <t>8b488ee9-1043-48ed-8fe9-3247aa2ddee3</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
+      <c r="AA127" t="inlineStr">
         <is>
           <t>a298b6ea-b0a3-4f24-9d22-7061e232a5a0</t>
         </is>
@@ -11211,17 +11277,17 @@
           <t>[!][!]</t>
         </is>
       </c>
-      <c r="X128" t="inlineStr">
+      <c r="Y128" t="inlineStr">
         <is>
           <t>89c9dc59-6f45-4417-8ba8-b4eac0d1431d</t>
         </is>
       </c>
-      <c r="Y128" t="inlineStr">
+      <c r="Z128" t="inlineStr">
         <is>
           <t>bbb5a006-5c54-447d-862b-460bbcfe17f5</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
+      <c r="AA128" t="inlineStr">
         <is>
           <t>a298b6ea-b0a3-4f24-9d22-7061e232a5a0</t>
         </is>
@@ -11308,12 +11374,12 @@
           <t>JG</t>
         </is>
       </c>
-      <c r="X129" t="inlineStr">
+      <c r="Y129" t="inlineStr">
         <is>
           <t>de620607-28fd-4c3c-aad8-03448edf9914</t>
         </is>
       </c>
-      <c r="Y129" t="inlineStr">
+      <c r="Z129" t="inlineStr">
         <is>
           <t>67a3cbbe-4feb-4964-abe0-802ee36b53e6</t>
         </is>
@@ -11405,12 +11471,12 @@
           <t>Only juggles in close range on a standing opponent.</t>
         </is>
       </c>
-      <c r="X130" t="inlineStr">
+      <c r="Y130" t="inlineStr">
         <is>
           <t>b61e7c91-c0b1-41cb-8bae-0f838b5c3920</t>
         </is>
       </c>
-      <c r="Y130" t="inlineStr">
+      <c r="Z130" t="inlineStr">
         <is>
           <t>ad152d54-9060-48a2-8068-792807ee613b</t>
         </is>
@@ -11542,20 +11608,25 @@
       </c>
       <c r="X133" s="1" t="inlineStr">
         <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Y133" s="1" t="inlineStr">
+        <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Y133" s="1" t="inlineStr">
+      <c r="Z133" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Z133" s="1" t="inlineStr">
+      <c r="AA133" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AA133" s="1" t="inlineStr">
+      <c r="AB133" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -11597,12 +11668,12 @@
           <t>hmmhhLm[!][!]!</t>
         </is>
       </c>
-      <c r="Y134" t="inlineStr">
+      <c r="Z134" t="inlineStr">
         <is>
           <t>7a24210e-7ae9-446c-a303-2ad7eba2ac12</t>
         </is>
       </c>
-      <c r="AA134" t="inlineStr">
+      <c r="AB134" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -11644,12 +11715,12 @@
           <t>hmmhmmmm[!]!</t>
         </is>
       </c>
-      <c r="Y135" t="inlineStr">
+      <c r="Z135" t="inlineStr">
         <is>
           <t>e7491c61-b40c-4c01-87b6-9b84db2d350e</t>
         </is>
       </c>
-      <c r="AA135" t="inlineStr">
+      <c r="AB135" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -11691,12 +11762,12 @@
           <t>hhmhhLm[!][!]!</t>
         </is>
       </c>
-      <c r="Y136" t="inlineStr">
+      <c r="Z136" t="inlineStr">
         <is>
           <t>51b32f66-b200-49c0-ad4b-c52c71e51bcd</t>
         </is>
       </c>
-      <c r="AA136" t="inlineStr">
+      <c r="AB136" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -11738,12 +11809,12 @@
           <t>hmmhhLmm</t>
         </is>
       </c>
-      <c r="Y137" t="inlineStr">
+      <c r="Z137" t="inlineStr">
         <is>
           <t>11bf5f22-1ce6-4a60-a66b-d9ef064953bb</t>
         </is>
       </c>
-      <c r="AA137" t="inlineStr">
+      <c r="AB137" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -11785,12 +11856,12 @@
           <t>hhmhhLmm</t>
         </is>
       </c>
-      <c r="Y138" t="inlineStr">
+      <c r="Z138" t="inlineStr">
         <is>
           <t>9b6d5b1e-d48e-46f1-b1c7-21d5b7e3d2e1</t>
         </is>
       </c>
-      <c r="AA138" t="inlineStr">
+      <c r="AB138" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -11832,12 +11903,12 @@
           <t>hhmh!</t>
         </is>
       </c>
-      <c r="Y139" t="inlineStr">
+      <c r="Z139" t="inlineStr">
         <is>
           <t>1d6b4525-e2f5-45b8-b095-3e41e4cec56b</t>
         </is>
       </c>
-      <c r="AA139" t="inlineStr">
+      <c r="AB139" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -11879,12 +11950,12 @@
           <t>hhmh!</t>
         </is>
       </c>
-      <c r="Y140" t="inlineStr">
+      <c r="Z140" t="inlineStr">
         <is>
           <t>d39521f6-f2ff-4975-8663-4aac08ebeffc</t>
         </is>
       </c>
-      <c r="AA140" t="inlineStr">
+      <c r="AB140" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>

--- a/sources/yoshimitsu_step7.xlsx
+++ b/sources/yoshimitsu_step7.xlsx
@@ -437,7 +437,7 @@
     <col width="24" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="25" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>ms[!]</t>
+          <t>ms!</t>
         </is>
       </c>
       <c r="Y83" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Y106" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>[!][!]</t>
+          <t>!!</t>
         </is>
       </c>
       <c r="Y107" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>[!][!]</t>
+          <t>!!</t>
         </is>
       </c>
       <c r="Y108" t="inlineStr">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>[!]h</t>
+          <t>!h</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
@@ -9753,7 +9753,7 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>[!]-</t>
+          <t>!-</t>
         </is>
       </c>
       <c r="W110" t="inlineStr">
@@ -9860,7 +9860,7 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>[!]m</t>
+          <t>!m</t>
         </is>
       </c>
       <c r="V111" t="inlineStr">
@@ -10081,12 +10081,12 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>!![!]</t>
+          <t>!!!</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>!![!]</t>
+          <t>!!!</t>
         </is>
       </c>
       <c r="Y114" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>m[!]</t>
+          <t>m!</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>m[!]</t>
+          <t>m!</t>
         </is>
       </c>
       <c r="Y115" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Y123" t="inlineStr">
@@ -10921,7 +10921,7 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>[!]-</t>
+          <t>!-</t>
         </is>
       </c>
       <c r="Y124" t="inlineStr">
@@ -10993,12 +10993,12 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>[!]-[!]</t>
+          <t>!-!</t>
         </is>
       </c>
       <c r="W125" t="inlineStr">
@@ -11090,12 +11090,12 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Y126" t="inlineStr">
@@ -11177,12 +11177,12 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>[!][!]</t>
+          <t>!!</t>
         </is>
       </c>
       <c r="Y127" t="inlineStr">
@@ -11269,12 +11269,12 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>[!][!]</t>
+          <t>!!</t>
         </is>
       </c>
       <c r="Y128" t="inlineStr">
@@ -11660,12 +11660,12 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>hmmhhLm[!][!]!</t>
+          <t>hmmhhLm!!!</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>hmmhhLm[!][!]!</t>
+          <t>hmmhhLm!!!</t>
         </is>
       </c>
       <c r="Z134" t="inlineStr">
@@ -11707,12 +11707,12 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>hmmhmmmm[!]!</t>
+          <t>hmmhmmmm!!</t>
         </is>
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>hmmhmmmm[!]!</t>
+          <t>hmmhmmmm!!</t>
         </is>
       </c>
       <c r="Z135" t="inlineStr">
@@ -11754,12 +11754,12 @@
       </c>
       <c r="R136" t="inlineStr">
         <is>
-          <t>hhmhhLm[!][!]!</t>
+          <t>hhmhhLm!!!</t>
         </is>
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>hhmhhLm[!][!]!</t>
+          <t>hhmhhLm!!!</t>
         </is>
       </c>
       <c r="Z136" t="inlineStr">

--- a/sources/yoshimitsu_step7.xlsx
+++ b/sources/yoshimitsu_step7.xlsx
@@ -851,6 +851,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>354a3fa8-57b9-4015-af73-fbbd2a144a43</t>
+        </is>
+      </c>
       <c r="Z6" t="inlineStr">
         <is>
           <t>354a3fa8-57b9-4015-af73-fbbd2a144a43</t>
@@ -913,6 +918,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>20aa9f1d-6b31-434f-844f-26957fc46e7e</t>
+        </is>
+      </c>
       <c r="Z7" t="inlineStr">
         <is>
           <t>20aa9f1d-6b31-434f-844f-26957fc46e7e</t>
@@ -973,6 +983,11 @@
       <c r="U8" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>7e99b815-adc2-430a-a808-4fc52a37e967</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -11668,6 +11683,11 @@
           <t>hmmhhLm!!!</t>
         </is>
       </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>7a24210e-7ae9-446c-a303-2ad7eba2ac12</t>
+        </is>
+      </c>
       <c r="Z134" t="inlineStr">
         <is>
           <t>7a24210e-7ae9-446c-a303-2ad7eba2ac12</t>
@@ -11715,6 +11735,11 @@
           <t>hmmhmmmm!!</t>
         </is>
       </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>e7491c61-b40c-4c01-87b6-9b84db2d350e</t>
+        </is>
+      </c>
       <c r="Z135" t="inlineStr">
         <is>
           <t>e7491c61-b40c-4c01-87b6-9b84db2d350e</t>
@@ -11762,6 +11787,11 @@
           <t>hhmhhLm!!!</t>
         </is>
       </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>51b32f66-b200-49c0-ad4b-c52c71e51bcd</t>
+        </is>
+      </c>
       <c r="Z136" t="inlineStr">
         <is>
           <t>51b32f66-b200-49c0-ad4b-c52c71e51bcd</t>
@@ -11809,6 +11839,11 @@
           <t>hmmhhLmm</t>
         </is>
       </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>11bf5f22-1ce6-4a60-a66b-d9ef064953bb</t>
+        </is>
+      </c>
       <c r="Z137" t="inlineStr">
         <is>
           <t>11bf5f22-1ce6-4a60-a66b-d9ef064953bb</t>
@@ -11856,6 +11891,11 @@
           <t>hhmhhLmm</t>
         </is>
       </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>9b6d5b1e-d48e-46f1-b1c7-21d5b7e3d2e1</t>
+        </is>
+      </c>
       <c r="Z138" t="inlineStr">
         <is>
           <t>9b6d5b1e-d48e-46f1-b1c7-21d5b7e3d2e1</t>
@@ -11903,6 +11943,11 @@
           <t>hhmh!</t>
         </is>
       </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>1d6b4525-e2f5-45b8-b095-3e41e4cec56b</t>
+        </is>
+      </c>
       <c r="Z139" t="inlineStr">
         <is>
           <t>1d6b4525-e2f5-45b8-b095-3e41e4cec56b</t>
@@ -11948,6 +11993,11 @@
       <c r="S140" t="inlineStr">
         <is>
           <t>hhmh!</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>d39521f6-f2ff-4975-8663-4aac08ebeffc</t>
         </is>
       </c>
       <c r="Z140" t="inlineStr">
